--- a/ZiiPOS_MenuTemplate.xlsx
+++ b/ZiiPOS_MenuTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Nan_Dev\ZiiPOSMenuConvertor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nan_Dev\ZiiPOSMenuConvertor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82BA92F-5AE8-42DF-8359-18C228BC061F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C132CB0-DC69-4C54-A8B2-93A97AE932F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="24870" windowHeight="11295" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -696,9 +696,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -736,7 +736,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -842,7 +842,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -984,7 +984,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -993,14 +993,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1013,9 +1013,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -1061,9 +1061,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>190</v>
       </c>
@@ -1091,9 +1091,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -1124,9 +1124,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -1172,14 +1172,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1239,29 +1239,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1274,14 +1274,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1351,14 +1351,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="21" max="21" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>54</v>
       </c>
@@ -1535,9 +1535,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -1568,23 +1568,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:DS2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="21" max="21" width="16" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="106" max="106" width="18" bestFit="1" customWidth="1"/>
-    <col min="110" max="110" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="111" max="111" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="112" max="112" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="113" max="116" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="118" max="118" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="119" max="119" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="113" max="116" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="120" max="120" width="29" bestFit="1" customWidth="1"/>
-    <col min="121" max="121" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="122" max="122" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="7.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -1955,7 +1956,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>175</v>
       </c>
@@ -1975,16 +1976,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -2017,7 +2018,7 @@
         <v>1</v>
       </c>
       <c r="AA2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="b">
         <v>1</v>
@@ -2086,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="AX2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY2">
         <v>0</v>
@@ -2098,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC2">
         <v>0</v>
@@ -2283,9 +2284,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -2304,9 +2305,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>63</v>
       </c>
